--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57324</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2024 artfynd.xlsx
+++ b/artfynd/A 31060-2024 artfynd.xlsx
@@ -675,45 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119166349</v>
+        <v>119166404</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579446</v>
+        <v>579500</v>
       </c>
       <c r="R2" t="n">
-        <v>6426796</v>
+        <v>6426787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,51 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119166282</v>
+        <v>119166310</v>
       </c>
       <c r="B3" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579452</v>
+        <v>579451</v>
       </c>
       <c r="R3" t="n">
-        <v>6426814</v>
+        <v>6426820</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,16 +889,11 @@
         <v>119166387</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1018,12 +998,7 @@
         <v>119166382</v>
       </c>
       <c r="B5" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,50 +1104,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119166310</v>
+        <v>119166282</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579451</v>
+        <v>579452</v>
       </c>
       <c r="R6" t="n">
-        <v>6426820</v>
+        <v>6426814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,12 +1217,7 @@
         <v>119166329</v>
       </c>
       <c r="B7" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,41 +1320,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119166404</v>
+        <v>119166349</v>
       </c>
       <c r="B8" t="n">
-        <v>94679</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1398,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579500</v>
+        <v>579446</v>
       </c>
       <c r="R8" t="n">
-        <v>6426787</v>
+        <v>6426796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
